--- a/crm/v2/lgo/integral-top500-leo.xlsx
+++ b/crm/v2/lgo/integral-top500-leo.xlsx
@@ -533,7 +533,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>3474419</t>
+        </is>
+      </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>3400934744198</t>
@@ -571,7 +575,11 @@
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>4960553</t>
+        </is>
+      </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>3400949605538</t>
@@ -609,7 +617,11 @@
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3200509</t>
+        </is>
+      </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>3400932005093</t>
@@ -647,7 +659,11 @@
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>6223413</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -685,7 +701,11 @@
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>3324737</t>
+        </is>
+      </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>3400933247379</t>
@@ -723,7 +743,11 @@
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>3515495</t>
+        </is>
+      </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>3400935154958</t>
@@ -761,7 +785,11 @@
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>3098608</t>
+        </is>
+      </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>3400930986080</t>
@@ -799,7 +827,11 @@
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>3029291</t>
+        </is>
+      </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>3400930292914</t>
@@ -815,7 +847,7 @@
         <v>221.32</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>212.71</v>
+        <v>212.74</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -837,7 +869,11 @@
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2238562</t>
+        </is>
+      </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>3400922385624</t>
@@ -875,7 +911,11 @@
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>3290599</t>
+        </is>
+      </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>3400932905997</t>
@@ -913,7 +953,11 @@
       <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>3029290</t>
+        </is>
+      </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>3400930292907</t>
@@ -929,7 +973,7 @@
         <v>163.7</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>157.33</v>
+        <v>157.36</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -951,7 +995,11 @@
       <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>3443873</t>
+        </is>
+      </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>3400934438738</t>
@@ -989,7 +1037,11 @@
       <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>6042767</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -1027,7 +1079,11 @@
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>4066958</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -1065,7 +1121,11 @@
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>3216290</t>
+        </is>
+      </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>3400932162901</t>
@@ -1103,7 +1163,11 @@
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>3005620</t>
+        </is>
+      </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>3400930056202</t>
@@ -1119,7 +1183,7 @@
         <v>107.56</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>103.38</v>
+        <v>103.4</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -1141,7 +1205,11 @@
       <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>3138414</t>
+        </is>
+      </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>3400931384144</t>
@@ -1179,7 +1247,11 @@
       <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>3130737</t>
+        </is>
+      </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>3400931307372</t>
@@ -1217,7 +1289,11 @@
       <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>3552898</t>
+        </is>
+      </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>3400935528988</t>
@@ -1255,7 +1331,11 @@
       <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2686303</t>
+        </is>
+      </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>3400926863036</t>
@@ -1271,7 +1351,7 @@
         <v>73.34</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>70.48999999999999</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1293,7 +1373,11 @@
       <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>3267672</t>
+        </is>
+      </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>3400932676729</t>
@@ -1331,7 +1415,11 @@
       <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>3034844</t>
+        </is>
+      </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>3400930348444</t>
@@ -1369,7 +1457,11 @@
       <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>3186301</t>
+        </is>
+      </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>3400931863014</t>
@@ -1407,7 +1499,11 @@
       <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>3019275</t>
+        </is>
+      </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>3400930192757</t>
@@ -1445,7 +1541,11 @@
       <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>3309525</t>
+        </is>
+      </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>3400933095253</t>
@@ -1483,7 +1583,11 @@
       <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>3171050</t>
+        </is>
+      </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>3400931710509</t>
@@ -1521,7 +1625,11 @@
       <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>3535836</t>
+        </is>
+      </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>3400935358363</t>
@@ -1559,7 +1667,11 @@
       <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>3479670</t>
+        </is>
+      </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>3400934796708</t>
@@ -1597,7 +1709,11 @@
       <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>3234017</t>
+        </is>
+      </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>3400932340170</t>
@@ -1635,7 +1751,11 @@
       <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>3014186</t>
+        </is>
+      </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>3400930141861</t>
@@ -1651,7 +1771,7 @@
         <v>175.18</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>168.37</v>
+        <v>168.39</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1673,7 +1793,11 @@
       <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>3006555</t>
+        </is>
+      </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>3400930065556</t>
@@ -1711,7 +1835,11 @@
       <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>3030312</t>
+        </is>
+      </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>3400930303122</t>
@@ -1727,7 +1855,7 @@
         <v>366.23</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>351.98</v>
+        <v>352.02</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -1749,7 +1877,11 @@
       <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>3006578</t>
+        </is>
+      </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>3400930065785</t>
@@ -1787,7 +1919,11 @@
       <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>3625137</t>
+        </is>
+      </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>3400936251373</t>
@@ -1825,7 +1961,11 @@
       <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>3002858</t>
+        </is>
+      </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>3400930028582</t>
@@ -1841,7 +1981,7 @@
         <v>171.07</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>164.42</v>
+        <v>164.44</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -1863,7 +2003,11 @@
       <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>3778421</t>
+        </is>
+      </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>3400937784214</t>
@@ -1901,7 +2045,11 @@
       <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>6006071</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -1939,7 +2087,11 @@
       <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2673826</t>
+        </is>
+      </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>3400926738266</t>
@@ -1955,7 +2107,7 @@
         <v>7.62</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>7.32</v>
+        <v>7.33</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -1977,7 +2129,11 @@
       <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>3461546</t>
+        </is>
+      </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>3400934615467</t>
@@ -2015,7 +2171,11 @@
       <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2225720</t>
+        </is>
+      </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>3400922257204</t>
@@ -2053,7 +2213,11 @@
       <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>3006566</t>
+        </is>
+      </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>3400930065662</t>
@@ -2091,7 +2255,11 @@
       <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>3325406</t>
+        </is>
+      </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>3400933254063</t>
@@ -2129,7 +2297,11 @@
       <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>3006589</t>
+        </is>
+      </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>3400930065891</t>
@@ -2167,7 +2339,11 @@
       <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>9000008</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
@@ -2205,7 +2381,11 @@
       <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>3244079</t>
+        </is>
+      </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>3400932440795</t>
@@ -2243,7 +2423,11 @@
       <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>6223558</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
@@ -2281,7 +2465,11 @@
       <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>3029293</t>
+        </is>
+      </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>3400930292938</t>
@@ -2297,7 +2485,7 @@
         <v>313.27</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>301.08</v>
+        <v>301.11</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
@@ -2319,7 +2507,11 @@
       <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>3192750</t>
+        </is>
+      </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>3400931927501</t>
@@ -2357,7 +2549,11 @@
       <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>3535606</t>
+        </is>
+      </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>3400935356062</t>
@@ -2370,10 +2566,10 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>4.51</v>
+        <v>4.43</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
@@ -2395,7 +2591,11 @@
       <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>3024437</t>
+        </is>
+      </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>3400930244371</t>
@@ -2411,7 +2611,7 @@
         <v>45.12</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>43.36</v>
+        <v>43.39</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
@@ -2433,7 +2633,11 @@
       <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>3293534</t>
+        </is>
+      </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>3400932935345</t>
@@ -2471,7 +2675,11 @@
       <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>3464668</t>
+        </is>
+      </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>3400934646683</t>
@@ -2509,7 +2717,11 @@
       <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>3066933</t>
+        </is>
+      </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>3400930669334</t>
@@ -2547,7 +2759,11 @@
       <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>3687374</t>
+        </is>
+      </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>3400936873742</t>
@@ -2563,7 +2779,7 @@
         <v>19.92</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.15</v>
+        <v>19.17</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
@@ -2585,7 +2801,11 @@
       <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>3820382</t>
+        </is>
+      </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>3400938203820</t>
@@ -2623,7 +2843,11 @@
       <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>3351800</t>
+        </is>
+      </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>3400933518004</t>
@@ -2661,7 +2885,11 @@
       <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2225393</t>
+        </is>
+      </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>3400922253930</t>
@@ -2677,7 +2905,7 @@
         <v>36.18</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>34.77</v>
+        <v>34.8</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
@@ -2699,7 +2927,11 @@
       <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>3000376</t>
+        </is>
+      </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>3400930003763</t>
@@ -2715,7 +2947,7 @@
         <v>74.28</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>71.39</v>
+        <v>71.42</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
@@ -2737,7 +2969,11 @@
       <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>3015110</t>
+        </is>
+      </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>3400930151105</t>
@@ -2753,7 +2989,7 @@
         <v>70.98999999999999</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>68.23</v>
+        <v>68.25</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
@@ -2775,7 +3011,11 @@
       <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>3012140</t>
+        </is>
+      </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>3400930121405</t>
@@ -2813,7 +3053,11 @@
       <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>3218969</t>
+        </is>
+      </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>3400932189694</t>
@@ -2851,7 +3095,11 @@
       <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>3595583</t>
+        </is>
+      </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>3400935955838</t>
@@ -2889,7 +3137,11 @@
       <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>3113638</t>
+        </is>
+      </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>3400931136385</t>
@@ -2927,7 +3179,11 @@
       <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>3189363</t>
+        </is>
+      </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>3400931893639</t>
@@ -2965,7 +3221,11 @@
       <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>3025862</t>
+        </is>
+      </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>3400930258620</t>
@@ -2981,7 +3241,7 @@
         <v>136.5</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>131.19</v>
+        <v>131.21</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
@@ -3003,7 +3263,11 @@
       <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>3192253</t>
+        </is>
+      </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>3400931922537</t>
@@ -3041,7 +3305,11 @@
       <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>3006568</t>
+        </is>
+      </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>3400930065686</t>
@@ -3079,7 +3347,11 @@
       <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>3023000</t>
+        </is>
+      </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>3400930230008</t>
@@ -3117,7 +3389,11 @@
       <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>3233153</t>
+        </is>
+      </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>3400932331536</t>
@@ -3155,7 +3431,11 @@
       <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>3174284</t>
+        </is>
+      </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>3400931742845</t>
@@ -3193,7 +3473,11 @@
       <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>6311785</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
@@ -3231,7 +3515,11 @@
       <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>3006601</t>
+        </is>
+      </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>3400930066010</t>
@@ -3269,7 +3557,11 @@
       <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>3707125</t>
+        </is>
+      </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>3400937071253</t>
@@ -3307,7 +3599,11 @@
       <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>3158575</t>
+        </is>
+      </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>3400931585756</t>
@@ -3345,7 +3641,11 @@
       <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>3041867</t>
+        </is>
+      </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>3400930418673</t>
@@ -3361,7 +3661,7 @@
         <v>4.41</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
@@ -3383,7 +3683,11 @@
       <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>4153396</t>
+        </is>
+      </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>3400941533969</t>
@@ -3421,7 +3725,11 @@
       <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>3624698</t>
+        </is>
+      </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>3400936246980</t>
@@ -3459,7 +3767,11 @@
       <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>3026454</t>
+        </is>
+      </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>3400930264546</t>
@@ -3497,7 +3809,11 @@
       <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>3025866</t>
+        </is>
+      </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
           <t>3400930258668</t>
@@ -3513,7 +3829,7 @@
         <v>181.48</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>174.42</v>
+        <v>174.45</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
@@ -3535,7 +3851,11 @@
       <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>4168624</t>
+        </is>
+      </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
           <t>3400941686245</t>
@@ -3573,7 +3893,11 @@
       <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>3025864</t>
+        </is>
+      </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
           <t>3400930258644</t>
@@ -3589,7 +3913,7 @@
         <v>136.5</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>131.19</v>
+        <v>131.21</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
@@ -3611,7 +3935,11 @@
       <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>3513734</t>
+        </is>
+      </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
           <t>3400935137340</t>
@@ -3627,7 +3955,7 @@
         <v>11.84</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>11.38</v>
+        <v>11.4</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
@@ -3649,7 +3977,11 @@
       <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>3391308</t>
+        </is>
+      </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
           <t>3400933913083</t>
@@ -3687,7 +4019,11 @@
       <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>3747768</t>
+        </is>
+      </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
           <t>3400937477680</t>
@@ -3725,7 +4061,11 @@
       <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>3279066</t>
+        </is>
+      </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
           <t>3400932790661</t>
@@ -3763,7 +4103,11 @@
       <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>3021645</t>
+        </is>
+      </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
           <t>3400930216453</t>
@@ -3779,7 +4123,7 @@
         <v>74.28</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>71.39</v>
+        <v>71.42</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
@@ -3801,7 +4145,11 @@
       <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>3029294</t>
+        </is>
+      </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
           <t>3400930292945</t>
@@ -3817,7 +4165,7 @@
         <v>313.27</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>301.08</v>
+        <v>301.11</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
@@ -3839,7 +4187,11 @@
       <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>3135858</t>
+        </is>
+      </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
           <t>3400931358589</t>
@@ -3877,7 +4229,11 @@
       <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>3264550</t>
+        </is>
+      </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
           <t>3400932645503</t>
@@ -3915,7 +4271,11 @@
       <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>3023497</t>
+        </is>
+      </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
           <t>3400930234976</t>
@@ -3953,7 +4313,11 @@
       <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>3499945</t>
+        </is>
+      </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
           <t>3400934999451</t>
@@ -3991,7 +4355,11 @@
       <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>3105283</t>
+        </is>
+      </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
           <t>3400931052838</t>
@@ -4029,7 +4397,11 @@
       <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>3118794</t>
+        </is>
+      </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
           <t>3400931187943</t>
@@ -4067,7 +4439,11 @@
       <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>3006557</t>
+        </is>
+      </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
           <t>3400930065570</t>
@@ -4105,7 +4481,11 @@
       <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>3228577</t>
+        </is>
+      </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
           <t>3400932285778</t>
@@ -4121,7 +4501,7 @@
         <v>6.98</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>6.71</v>
+        <v>6.98</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
@@ -4143,7 +4523,11 @@
       <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>4066912</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
@@ -4181,7 +4565,11 @@
       <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>3008456</t>
+        </is>
+      </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
           <t>3400930084564</t>
@@ -4219,7 +4607,11 @@
       <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2217904</t>
+        </is>
+      </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
           <t>3400922179049</t>
@@ -4257,7 +4649,11 @@
       <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>3020488</t>
+        </is>
+      </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
           <t>3400930204887</t>
@@ -4295,7 +4691,11 @@
       <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>3021648</t>
+        </is>
+      </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
           <t>3400930216484</t>
@@ -4311,7 +4711,7 @@
         <v>74.28</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>71.39</v>
+        <v>71.42</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
@@ -4333,7 +4733,11 @@
       <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>3570614</t>
+        </is>
+      </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
           <t>3400935706140</t>
@@ -4371,7 +4775,11 @@
       <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>3026024</t>
+        </is>
+      </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
           <t>3400930260241</t>
@@ -4387,7 +4795,7 @@
         <v>157.37</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>151.25</v>
+        <v>151.27</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
@@ -4409,7 +4817,11 @@
       <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>3529422</t>
+        </is>
+      </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
           <t>3400935294227</t>
@@ -4447,7 +4859,11 @@
       <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>3189819</t>
+        </is>
+      </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
           <t>3400931898191</t>
@@ -4485,7 +4901,11 @@
       <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>3192767</t>
+        </is>
+      </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
           <t>3400931927679</t>
@@ -4523,7 +4943,11 @@
       <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>3348413</t>
+        </is>
+      </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
           <t>3400933484132</t>
@@ -4561,7 +4985,11 @@
       <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>3422397</t>
+        </is>
+      </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
           <t>3400934223976</t>
@@ -4599,7 +5027,11 @@
       <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2735007</t>
+        </is>
+      </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
           <t>3400927350078</t>
@@ -4615,7 +5047,7 @@
         <v>30.09</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>28.92</v>
+        <v>28.94</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
@@ -4637,7 +5069,11 @@
       <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>3480940</t>
+        </is>
+      </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
           <t>3400934809408</t>
@@ -4675,7 +5111,11 @@
       <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>3230829</t>
+        </is>
+      </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
           <t>3400932308293</t>
@@ -4713,7 +5153,11 @@
       <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>3446417</t>
+        </is>
+      </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
           <t>3400934464171</t>
@@ -4751,7 +5195,11 @@
       <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>3644146</t>
+        </is>
+      </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
           <t>3400936441460</t>
@@ -4789,7 +5237,11 @@
       <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>3153342</t>
+        </is>
+      </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
           <t>3400931533429</t>
@@ -4827,7 +5279,11 @@
       <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2669210</t>
+        </is>
+      </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
           <t>3400926692100</t>
@@ -4865,7 +5321,11 @@
       <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>3412594</t>
+        </is>
+      </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
           <t>3400934125942</t>
@@ -4903,7 +5363,11 @@
       <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>3001667</t>
+        </is>
+      </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
           <t>3400930016671</t>
@@ -4919,7 +5383,7 @@
         <v>32.31</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>31.05</v>
+        <v>31.08</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
@@ -4941,7 +5405,11 @@
       <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>5437210</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
@@ -4979,7 +5447,11 @@
       <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>3105308</t>
+        </is>
+      </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
           <t>3400931053088</t>
@@ -5017,7 +5489,11 @@
       <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>3140500</t>
+        </is>
+      </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
           <t>3400931405009</t>
@@ -5055,7 +5531,11 @@
       <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2788676</t>
+        </is>
+      </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
           <t>3400927886768</t>
@@ -5093,7 +5573,11 @@
       <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>3419538</t>
+        </is>
+      </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
           <t>3400934195389</t>
@@ -5131,7 +5615,11 @@
       <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>3019529</t>
+        </is>
+      </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
           <t>3400930195291</t>
@@ -5169,7 +5657,11 @@
       <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>3403589</t>
+        </is>
+      </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
           <t>3400934035890</t>
@@ -5207,7 +5699,11 @@
       <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2678410</t>
+        </is>
+      </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
           <t>3400926784102</t>
@@ -5245,7 +5741,11 @@
       <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>3023498</t>
+        </is>
+      </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
           <t>3400930234983</t>
@@ -5283,7 +5783,11 @@
       <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>3026231</t>
+        </is>
+      </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
           <t>3400930262313</t>
@@ -5321,7 +5825,11 @@
       <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>3005328</t>
+        </is>
+      </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
           <t>3400930053287</t>
@@ -5359,7 +5867,11 @@
       <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>3491240</t>
+        </is>
+      </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
           <t>3400934912405</t>
@@ -5397,7 +5909,11 @@
       <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>3012142</t>
+        </is>
+      </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
           <t>3400930121429</t>
@@ -5413,7 +5929,7 @@
         <v>4.72</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
@@ -5435,7 +5951,11 @@
       <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>3338461</t>
+        </is>
+      </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
           <t>3400933384616</t>
@@ -5473,7 +5993,11 @@
       <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>3015793</t>
+        </is>
+      </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
           <t>3400930157930</t>
@@ -5511,7 +6035,11 @@
       <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>3219294</t>
+        </is>
+      </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
           <t>3400932192946</t>
@@ -5549,7 +6077,11 @@
       <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr"/>
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>3232018</t>
+        </is>
+      </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
           <t>3400932320189</t>
@@ -5587,7 +6119,11 @@
       <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>3003791</t>
+        </is>
+      </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
           <t>3400930037911</t>
@@ -5625,7 +6161,11 @@
       <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>3442307</t>
+        </is>
+      </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
           <t>3400934423079</t>
@@ -5663,7 +6203,11 @@
       <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>3162329</t>
+        </is>
+      </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
           <t>3400931623298</t>
@@ -5701,7 +6245,11 @@
       <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>3003790</t>
+        </is>
+      </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
           <t>3400930037904</t>
@@ -5777,7 +6325,11 @@
       <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2685798</t>
+        </is>
+      </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
           <t>3400926857981</t>
@@ -5793,7 +6345,7 @@
         <v>51.83</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>49.81</v>
+        <v>49.84</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
@@ -5815,7 +6367,11 @@
       <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>3024785</t>
+        </is>
+      </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
           <t>3400930247853</t>
@@ -5831,7 +6387,7 @@
         <v>52.31</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>50.28</v>
+        <v>50.3</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
@@ -5853,7 +6409,11 @@
       <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>3677387</t>
+        </is>
+      </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
           <t>3400936773875</t>
@@ -5869,7 +6429,7 @@
         <v>19.92</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>19.15</v>
+        <v>19.17</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
@@ -5891,7 +6451,11 @@
       <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr"/>
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>3772298</t>
+        </is>
+      </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
           <t>3400937722988</t>
@@ -5907,7 +6471,7 @@
         <v>33.59</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>32.28</v>
+        <v>32.31</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
@@ -5929,7 +6493,11 @@
       <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>3450778</t>
+        </is>
+      </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
           <t>3400934507786</t>
@@ -5967,7 +6535,11 @@
       <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr"/>
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>3015849</t>
+        </is>
+      </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
           <t>3400930158494</t>
@@ -6005,7 +6577,11 @@
       <c r="P145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>3295510</t>
+        </is>
+      </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
           <t>3400932955107</t>
@@ -6043,7 +6619,11 @@
       <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>3480986</t>
+        </is>
+      </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
           <t>3400934809866</t>
@@ -6081,7 +6661,11 @@
       <c r="P147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>3003792</t>
+        </is>
+      </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
           <t>3400930037928</t>
@@ -6119,7 +6703,11 @@
       <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr"/>
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>3031116</t>
+        </is>
+      </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
           <t>3400930311165</t>
@@ -6157,7 +6745,11 @@
       <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr"/>
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>7800001</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" s="2" t="inlineStr">
         <is>
@@ -6195,7 +6787,11 @@
       <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>3057302</t>
+        </is>
+      </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
           <t>3400930573020</t>
@@ -6233,7 +6829,11 @@
       <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr"/>
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>3006618</t>
+        </is>
+      </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
           <t>3400930066188</t>
@@ -6271,7 +6871,11 @@
       <c r="P152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr"/>
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>3207026</t>
+        </is>
+      </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
           <t>3400932070268</t>
@@ -6309,7 +6913,11 @@
       <c r="P153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr"/>
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>3015804</t>
+        </is>
+      </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
           <t>3400930158043</t>
@@ -6347,7 +6955,11 @@
       <c r="P154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr"/>
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>3641662</t>
+        </is>
+      </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
           <t>3400936416628</t>
@@ -6385,7 +6997,11 @@
       <c r="P155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>3768902</t>
+        </is>
+      </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
           <t>3400937689021</t>
@@ -6423,7 +7039,11 @@
       <c r="P156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>3039698</t>
+        </is>
+      </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
           <t>3400930396988</t>
@@ -6461,7 +7081,11 @@
       <c r="P157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>3027121</t>
+        </is>
+      </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
           <t>3400930271216</t>
@@ -6499,7 +7123,11 @@
       <c r="P158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr"/>
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>3025251</t>
+        </is>
+      </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
           <t>3400930252512</t>
@@ -6537,7 +7165,11 @@
       <c r="P159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>3113644</t>
+        </is>
+      </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
           <t>3400931136446</t>
@@ -6575,7 +7207,11 @@
       <c r="P160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr"/>
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2761996</t>
+        </is>
+      </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
           <t>3400927619960</t>
@@ -6613,7 +7249,11 @@
       <c r="P161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr"/>
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>3010861</t>
+        </is>
+      </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
           <t>3400930108611</t>
@@ -6651,7 +7291,11 @@
       <c r="P162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr"/>
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>3480911</t>
+        </is>
+      </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
           <t>3400934809118</t>
@@ -6689,7 +7333,11 @@
       <c r="P163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>3014595</t>
+        </is>
+      </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
           <t>3400930145951</t>
@@ -6727,7 +7375,11 @@
       <c r="P164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>3204654</t>
+        </is>
+      </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
           <t>3400932046546</t>
@@ -6765,7 +7417,11 @@
       <c r="P165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr"/>
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>3024059</t>
+        </is>
+      </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
           <t>3400930240595</t>
@@ -6781,7 +7437,7 @@
         <v>9.35</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>8.99</v>
+        <v>8.98</v>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
@@ -6803,7 +7459,11 @@
       <c r="P166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr"/>
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>3339756</t>
+        </is>
+      </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
           <t>3400933397562</t>
@@ -6841,7 +7501,11 @@
       <c r="P167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr"/>
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>3027120</t>
+        </is>
+      </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
           <t>3400930271209</t>
@@ -6879,7 +7543,11 @@
       <c r="P168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>4925031</t>
+        </is>
+      </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
           <t>3400949250318</t>
@@ -6895,7 +7563,7 @@
         <v>4.42</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
@@ -6917,7 +7585,11 @@
       <c r="P169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr"/>
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>3025863</t>
+        </is>
+      </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
           <t>3400930258637</t>
@@ -6933,7 +7605,7 @@
         <v>136.5</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>131.19</v>
+        <v>131.21</v>
       </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
@@ -6955,7 +7627,11 @@
       <c r="P170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>4194567</t>
+        </is>
+      </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
           <t>3400941945670</t>
@@ -6993,7 +7669,11 @@
       <c r="P171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr"/>
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>3007978</t>
+        </is>
+      </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
           <t>3400930079782</t>
@@ -7009,7 +7689,7 @@
         <v>29.5</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>28.35</v>
+        <v>28.38</v>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
@@ -7031,7 +7711,11 @@
       <c r="P172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>3149978</t>
+        </is>
+      </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
           <t>3400931499787</t>
@@ -7069,7 +7753,11 @@
       <c r="P173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr"/>
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>3002411</t>
+        </is>
+      </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
           <t>3400930024119</t>
@@ -7107,7 +7795,11 @@
       <c r="P174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr"/>
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2675268</t>
+        </is>
+      </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
           <t>3400926752682</t>
@@ -7145,7 +7837,11 @@
       <c r="P175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr"/>
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>3065253</t>
+        </is>
+      </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
           <t>3400930652534</t>
@@ -7183,7 +7879,11 @@
       <c r="P176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>3588755</t>
+        </is>
+      </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
           <t>3400935887559</t>
@@ -7221,7 +7921,11 @@
       <c r="P177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr"/>
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>3031324</t>
+        </is>
+      </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
           <t>3400930313244</t>
@@ -7259,7 +7963,11 @@
       <c r="P178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr"/>
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>3004007</t>
+        </is>
+      </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
           <t>3400930040072</t>
@@ -7275,7 +7983,7 @@
         <v>31.19</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>29.98</v>
+        <v>30</v>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
@@ -7297,7 +8005,11 @@
       <c r="P179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr"/>
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>3516690</t>
+        </is>
+      </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
           <t>3400935166906</t>
@@ -7313,7 +8025,7 @@
         <v>14.5</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>13.94</v>
+        <v>13.96</v>
       </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
@@ -7335,7 +8047,11 @@
       <c r="P180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr"/>
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>3263711</t>
+        </is>
+      </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
           <t>3400932637119</t>
@@ -7373,7 +8089,11 @@
       <c r="P181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr"/>
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>3032215</t>
+        </is>
+      </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
           <t>3400930322154</t>
@@ -7389,7 +8109,7 @@
         <v>70.98999999999999</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>68.23</v>
+        <v>68.25</v>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
@@ -7411,7 +8131,11 @@
       <c r="P182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr"/>
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>3248781</t>
+        </is>
+      </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
           <t>3400932487813</t>
@@ -7449,7 +8173,11 @@
       <c r="P183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr"/>
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>3442997</t>
+        </is>
+      </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
           <t>3400934429972</t>
@@ -7487,7 +8215,11 @@
       <c r="P184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr"/>
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>3301802</t>
+        </is>
+      </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
           <t>3400933018023</t>
@@ -7525,7 +8257,11 @@
       <c r="P185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr"/>
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>3274850</t>
+        </is>
+      </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
           <t>3400932748501</t>
@@ -7563,7 +8299,11 @@
       <c r="P186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr"/>
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>3649793</t>
+        </is>
+      </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
           <t>3400936497931</t>
@@ -7601,7 +8341,11 @@
       <c r="P187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr"/>
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>3063219</t>
+        </is>
+      </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
           <t>3400930632192</t>
@@ -7639,7 +8383,11 @@
       <c r="P188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr"/>
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>3707102</t>
+        </is>
+      </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
           <t>3400937071024</t>
@@ -7715,7 +8463,11 @@
       <c r="P190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr"/>
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>3285552</t>
+        </is>
+      </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
           <t>3400932855520</t>
@@ -7753,7 +8505,11 @@
       <c r="P191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr"/>
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>3278173</t>
+        </is>
+      </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
           <t>3400932781737</t>
@@ -7791,7 +8547,11 @@
       <c r="P192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr"/>
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>3636684</t>
+        </is>
+      </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
           <t>3400936366848</t>
@@ -7829,7 +8589,11 @@
       <c r="P193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr"/>
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>3239948</t>
+        </is>
+      </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
           <t>3400932399482</t>
@@ -7867,7 +8631,11 @@
       <c r="P194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr"/>
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>3481017</t>
+        </is>
+      </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
           <t>3400934810176</t>
@@ -7905,7 +8673,11 @@
       <c r="P195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>6025385</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" s="2" t="inlineStr">
         <is>
@@ -7943,7 +8715,11 @@
       <c r="P196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr"/>
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>3222379</t>
+        </is>
+      </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
           <t>3400932223794</t>
@@ -7981,7 +8757,11 @@
       <c r="P197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr"/>
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>3413613</t>
+        </is>
+      </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
           <t>3400934136139</t>
@@ -8019,7 +8799,11 @@
       <c r="P198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr"/>
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>3691849</t>
+        </is>
+      </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
           <t>3400936918498</t>
@@ -8057,7 +8841,11 @@
       <c r="P199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr"/>
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2795647</t>
+        </is>
+      </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
           <t>3400927956478</t>
@@ -8095,7 +8883,11 @@
       <c r="P200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr"/>
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>3012144</t>
+        </is>
+      </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
           <t>3400930121443</t>
@@ -8133,7 +8925,11 @@
       <c r="P201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr"/>
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>3331677</t>
+        </is>
+      </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
           <t>3400933316778</t>
@@ -8171,7 +8967,11 @@
       <c r="P202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr"/>
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>3051417</t>
+        </is>
+      </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
           <t>3400930514177</t>
@@ -8209,7 +9009,11 @@
       <c r="P203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr"/>
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>3027029</t>
+        </is>
+      </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
           <t>3400930270295</t>
@@ -8247,7 +9051,11 @@
       <c r="P204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr"/>
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>3372848</t>
+        </is>
+      </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
           <t>3400933728489</t>
@@ -8285,7 +9093,11 @@
       <c r="P205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr"/>
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>3235086</t>
+        </is>
+      </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
           <t>3400932350865</t>
@@ -8323,7 +9135,11 @@
       <c r="P206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr"/>
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>3741518</t>
+        </is>
+      </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
           <t>3400937415187</t>
@@ -8361,7 +9177,11 @@
       <c r="P207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr"/>
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>3001406</t>
+        </is>
+      </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
           <t>3400930014066</t>
@@ -8399,7 +9219,11 @@
       <c r="P208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr"/>
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>3015109</t>
+        </is>
+      </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
           <t>3400930151099</t>
@@ -8415,7 +9239,7 @@
         <v>70.98999999999999</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>68.23</v>
+        <v>68.25</v>
       </c>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
@@ -8437,7 +9261,11 @@
       <c r="P209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr"/>
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>3015795</t>
+        </is>
+      </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
           <t>3400930157954</t>
@@ -8475,7 +9303,11 @@
       <c r="P210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr"/>
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>3296449</t>
+        </is>
+      </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
           <t>3400932964499</t>
@@ -8513,7 +9345,11 @@
       <c r="P211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr"/>
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>3406435</t>
+        </is>
+      </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
           <t>3400934064357</t>
@@ -8551,7 +9387,11 @@
       <c r="P212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr"/>
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>3565607</t>
+        </is>
+      </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
           <t>3400935656070</t>
@@ -8589,7 +9429,11 @@
       <c r="P213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr"/>
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>3372736</t>
+        </is>
+      </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
           <t>3400933727369</t>
@@ -8605,7 +9449,7 @@
         <v>9.93</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
@@ -8627,7 +9471,11 @@
       <c r="P214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr"/>
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>3030527</t>
+        </is>
+      </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
           <t>3400930305270</t>
@@ -8665,7 +9513,11 @@
       <c r="P215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr"/>
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>3442402</t>
+        </is>
+      </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
           <t>3400934424021</t>
@@ -8703,7 +9555,11 @@
       <c r="P216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr"/>
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>3011979</t>
+        </is>
+      </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
           <t>3400930119792</t>
@@ -8741,7 +9597,11 @@
       <c r="P217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr"/>
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>3051268</t>
+        </is>
+      </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
           <t>3400930512685</t>
@@ -8779,7 +9639,11 @@
       <c r="P218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr"/>
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>3001395</t>
+        </is>
+      </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
           <t>3400930013953</t>
@@ -8817,7 +9681,11 @@
       <c r="P219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr"/>
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>3687463</t>
+        </is>
+      </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
           <t>3400936874633</t>
@@ -8833,7 +9701,7 @@
         <v>11.94</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>11.48</v>
+        <v>11.5</v>
       </c>
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
@@ -8855,7 +9723,11 @@
       <c r="P220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr"/>
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>3009564</t>
+        </is>
+      </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
           <t>3400930095645</t>
@@ -8893,7 +9765,11 @@
       <c r="P221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr"/>
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>3832244</t>
+        </is>
+      </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
           <t>3400938322446</t>
@@ -8931,7 +9807,11 @@
       <c r="P222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr"/>
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>3171481</t>
+        </is>
+      </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
           <t>3400931714811</t>
@@ -8969,7 +9849,11 @@
       <c r="P223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr"/>
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>3095969</t>
+        </is>
+      </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
           <t>3400930959695</t>
@@ -9007,7 +9891,11 @@
       <c r="P224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr"/>
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>3432616</t>
+        </is>
+      </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
           <t>3400934326165</t>
@@ -9045,7 +9933,11 @@
       <c r="P225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr"/>
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>3574693</t>
+        </is>
+      </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
           <t>3400935746931</t>
@@ -9083,7 +9975,11 @@
       <c r="P226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr"/>
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>7631235</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr"/>
       <c r="C227" s="2" t="inlineStr">
         <is>
@@ -9121,7 +10017,11 @@
       <c r="P227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr"/>
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>3314526</t>
+        </is>
+      </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
           <t>3400933145262</t>
@@ -9159,7 +10059,11 @@
       <c r="P228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr"/>
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>3490387</t>
+        </is>
+      </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
           <t>3400934903878</t>
@@ -9197,7 +10101,11 @@
       <c r="P229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr"/>
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>3247333</t>
+        </is>
+      </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
           <t>3400932473335</t>
@@ -9235,7 +10143,11 @@
       <c r="P230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr"/>
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>3305421</t>
+        </is>
+      </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
           <t>3400933054212</t>
@@ -9273,7 +10185,11 @@
       <c r="P231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr"/>
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>3057325</t>
+        </is>
+      </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
           <t>3400930573259</t>
@@ -9311,7 +10227,11 @@
       <c r="P232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr"/>
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>3015107</t>
+        </is>
+      </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
           <t>3400930151075</t>
@@ -9327,7 +10247,7 @@
         <v>70.98999999999999</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>68.23</v>
+        <v>68.25</v>
       </c>
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
@@ -9349,7 +10269,11 @@
       <c r="P233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr"/>
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>3902022</t>
+        </is>
+      </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
           <t>3400939020228</t>
@@ -9365,7 +10289,7 @@
         <v>54.1</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>52</v>
+        <v>52.02</v>
       </c>
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
@@ -9387,7 +10311,11 @@
       <c r="P234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr"/>
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>3851098</t>
+        </is>
+      </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
           <t>3400938510980</t>
@@ -9403,7 +10331,7 @@
         <v>25.97</v>
       </c>
       <c r="F235" s="3" t="n">
-        <v>24.96</v>
+        <v>24.99</v>
       </c>
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
@@ -9425,7 +10353,11 @@
       <c r="P235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr"/>
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>3000373</t>
+        </is>
+      </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
           <t>3400930003732</t>
@@ -9441,7 +10373,7 @@
         <v>74.28</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>71.39</v>
+        <v>71.42</v>
       </c>
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
@@ -9463,7 +10395,11 @@
       <c r="P236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr"/>
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>3375367</t>
+        </is>
+      </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
           <t>3400933753672</t>
@@ -9501,7 +10437,11 @@
       <c r="P237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr"/>
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>3207061</t>
+        </is>
+      </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
           <t>3400932070619</t>
@@ -9539,7 +10479,11 @@
       <c r="P238" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr"/>
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>3282565</t>
+        </is>
+      </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
           <t>3400932825653</t>
@@ -9577,7 +10521,11 @@
       <c r="P239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr"/>
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>3383088</t>
+        </is>
+      </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
           <t>3400933830885</t>
@@ -9615,7 +10563,11 @@
       <c r="P240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr"/>
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>3199410</t>
+        </is>
+      </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
           <t>3400931994107</t>
@@ -9653,7 +10605,11 @@
       <c r="P241" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr"/>
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2243971</t>
+        </is>
+      </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
           <t>3400922439716</t>
@@ -9691,7 +10647,11 @@
       <c r="P242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr"/>
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>3051558</t>
+        </is>
+      </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
           <t>3400930515587</t>
@@ -9729,7 +10689,11 @@
       <c r="P243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr"/>
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>3228502</t>
+        </is>
+      </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
           <t>3400932285020</t>
@@ -9767,7 +10731,11 @@
       <c r="P244" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr"/>
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>3600901</t>
+        </is>
+      </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
           <t>3400936009011</t>
@@ -9805,7 +10773,11 @@
       <c r="P245" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr"/>
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>2802577</t>
+        </is>
+      </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
           <t>3400928025777</t>
@@ -9843,7 +10815,11 @@
       <c r="P246" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr"/>
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>3377515</t>
+        </is>
+      </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
           <t>3400933775155</t>
@@ -9859,7 +10835,7 @@
         <v>19.65</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>18.89</v>
+        <v>18.91</v>
       </c>
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
@@ -9881,7 +10857,11 @@
       <c r="P247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr"/>
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>3521142</t>
+        </is>
+      </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
           <t>3400935211422</t>
@@ -9919,7 +10899,11 @@
       <c r="P248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr"/>
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>3011980</t>
+        </is>
+      </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
           <t>3400930119808</t>
@@ -9957,7 +10941,11 @@
       <c r="P249" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr"/>
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>3359049</t>
+        </is>
+      </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
           <t>3400933590499</t>
@@ -9973,7 +10961,7 @@
         <v>16.95</v>
       </c>
       <c r="F250" s="3" t="n">
-        <v>16.29</v>
+        <v>16.31</v>
       </c>
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
@@ -9995,7 +10983,11 @@
       <c r="P250" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr"/>
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>3028884</t>
+        </is>
+      </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
           <t>3400930288849</t>
@@ -10033,7 +11025,11 @@
       <c r="P251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr"/>
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>3205441</t>
+        </is>
+      </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
           <t>3400932054411</t>
@@ -10071,7 +11067,11 @@
       <c r="P252" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr"/>
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>3057319</t>
+        </is>
+      </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
           <t>3400930573198</t>
@@ -10109,7 +11109,11 @@
       <c r="P253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr"/>
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>3008316</t>
+        </is>
+      </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
           <t>3400930083161</t>
@@ -10125,7 +11129,7 @@
         <v>28.78</v>
       </c>
       <c r="F254" s="3" t="n">
-        <v>27.66</v>
+        <v>27.69</v>
       </c>
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
@@ -10147,7 +11151,11 @@
       <c r="P254" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr"/>
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>3327782</t>
+        </is>
+      </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
           <t>3400933277826</t>
@@ -10185,7 +11193,11 @@
       <c r="P255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr"/>
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>2110431</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr"/>
       <c r="C256" s="2" t="inlineStr">
         <is>
@@ -10223,7 +11235,11 @@
       <c r="P256" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr"/>
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>3552740</t>
+        </is>
+      </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
           <t>3400935527400</t>
@@ -10239,7 +11255,7 @@
         <v>20.39</v>
       </c>
       <c r="F257" s="3" t="n">
-        <v>19.6</v>
+        <v>19.62</v>
       </c>
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
@@ -10261,7 +11277,11 @@
       <c r="P257" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr"/>
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>3139543</t>
+        </is>
+      </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
           <t>3400931395430</t>
@@ -10299,7 +11319,11 @@
       <c r="P258" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr"/>
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>3137633</t>
+        </is>
+      </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
           <t>3400931376330</t>
@@ -10337,7 +11361,11 @@
       <c r="P259" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr"/>
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>5433102</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr"/>
       <c r="C260" s="2" t="inlineStr">
         <is>
@@ -10375,7 +11403,11 @@
       <c r="P260" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr"/>
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>3348904</t>
+        </is>
+      </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
           <t>3400933489045</t>
@@ -10413,7 +11445,11 @@
       <c r="P261" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr"/>
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>3909490</t>
+        </is>
+      </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
           <t>3400939094908</t>
@@ -10451,7 +11487,11 @@
       <c r="P262" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr"/>
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>3636661</t>
+        </is>
+      </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
           <t>3400936366619</t>
@@ -10489,7 +11529,11 @@
       <c r="P263" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr"/>
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>3353153</t>
+        </is>
+      </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
           <t>3400933531539</t>
@@ -10527,7 +11571,11 @@
       <c r="P264" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr"/>
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>3820034</t>
+        </is>
+      </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
           <t>3400938200348</t>
@@ -10565,7 +11613,11 @@
       <c r="P265" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr"/>
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>3298431</t>
+        </is>
+      </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
           <t>3400932984312</t>
@@ -10603,7 +11655,11 @@
       <c r="P266" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr"/>
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>3182409</t>
+        </is>
+      </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
           <t>3400931824091</t>
@@ -10641,7 +11697,11 @@
       <c r="P267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr"/>
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>3293698</t>
+        </is>
+      </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
           <t>3400932936984</t>
@@ -10679,7 +11739,11 @@
       <c r="P268" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr"/>
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>3314874</t>
+        </is>
+      </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
           <t>3400933148744</t>
@@ -10717,7 +11781,11 @@
       <c r="P269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr"/>
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>3356358</t>
+        </is>
+      </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
           <t>3400933563585</t>
@@ -10755,7 +11823,11 @@
       <c r="P270" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr"/>
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>3649899</t>
+        </is>
+      </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
           <t>3400936498990</t>
@@ -10793,7 +11865,11 @@
       <c r="P271" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr"/>
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>3675879</t>
+        </is>
+      </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
           <t>3400936758797</t>
@@ -10869,7 +11945,11 @@
       <c r="P273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr"/>
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>3006624</t>
+        </is>
+      </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
           <t>3400930066249</t>
@@ -10907,7 +11987,11 @@
       <c r="P274" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr"/>
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>3770135</t>
+        </is>
+      </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
           <t>3400937701358</t>
@@ -10945,7 +12029,11 @@
       <c r="P275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr"/>
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>3525909</t>
+        </is>
+      </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
           <t>3400935259097</t>
@@ -10961,7 +12049,7 @@
         <v>11.78</v>
       </c>
       <c r="F276" s="3" t="n">
-        <v>11.32</v>
+        <v>11.35</v>
       </c>
       <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr"/>
@@ -10983,7 +12071,11 @@
       <c r="P276" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr"/>
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>3015807</t>
+        </is>
+      </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
           <t>3400930158074</t>
@@ -10999,7 +12091,7 @@
         <v>5.28</v>
       </c>
       <c r="F277" s="3" t="n">
-        <v>5.07</v>
+        <v>5.08</v>
       </c>
       <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr"/>
@@ -11021,7 +12113,11 @@
       <c r="P277" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr"/>
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>3338308</t>
+        </is>
+      </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
           <t>3400933383084</t>
@@ -11097,7 +12193,11 @@
       <c r="P279" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr"/>
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>3218946</t>
+        </is>
+      </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
           <t>3400932189465</t>
@@ -11135,7 +12235,11 @@
       <c r="P280" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr"/>
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>3412565</t>
+        </is>
+      </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
           <t>3400934125652</t>
@@ -11173,7 +12277,11 @@
       <c r="P281" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr"/>
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>3690991</t>
+        </is>
+      </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
           <t>3400936909915</t>
@@ -11211,7 +12319,11 @@
       <c r="P282" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr"/>
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>3020642</t>
+        </is>
+      </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
           <t>3400930206423</t>
@@ -11249,7 +12361,11 @@
       <c r="P283" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr"/>
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>3644092</t>
+        </is>
+      </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
           <t>3400936440920</t>
@@ -11287,7 +12403,11 @@
       <c r="P284" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr"/>
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>3706829</t>
+        </is>
+      </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
           <t>3400937068291</t>
@@ -11325,7 +12445,11 @@
       <c r="P285" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr"/>
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>3025042</t>
+        </is>
+      </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
           <t>3400930250426</t>
@@ -11363,7 +12487,11 @@
       <c r="P286" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr"/>
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>2762010</t>
+        </is>
+      </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
           <t>3400927620102</t>
@@ -11401,7 +12529,11 @@
       <c r="P287" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr"/>
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>3001403</t>
+        </is>
+      </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
           <t>3400930014035</t>
@@ -11439,7 +12571,11 @@
       <c r="P288" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr"/>
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>3200805</t>
+        </is>
+      </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
           <t>3400932008056</t>
@@ -11455,7 +12591,7 @@
         <v>5.51</v>
       </c>
       <c r="F289" s="3" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr"/>
@@ -11477,7 +12613,11 @@
       <c r="P289" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr"/>
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>3029297</t>
+        </is>
+      </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
           <t>3400930292976</t>
@@ -11493,7 +12633,7 @@
         <v>404.83</v>
       </c>
       <c r="F290" s="3" t="n">
-        <v>389.08</v>
+        <v>389.11</v>
       </c>
       <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr"/>
@@ -11515,7 +12655,11 @@
       <c r="P290" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr"/>
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>3378348</t>
+        </is>
+      </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
           <t>3400933783488</t>
@@ -11553,7 +12697,11 @@
       <c r="P291" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr"/>
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>3019225</t>
+        </is>
+      </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
           <t>3400930192252</t>
@@ -11591,7 +12739,11 @@
       <c r="P292" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr"/>
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>3527989</t>
+        </is>
+      </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
           <t>3400935279897</t>
@@ -11629,7 +12781,11 @@
       <c r="P293" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr"/>
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>3678978</t>
+        </is>
+      </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
           <t>3400936789784</t>
@@ -11667,7 +12823,11 @@
       <c r="P294" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr"/>
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>3011977</t>
+        </is>
+      </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
           <t>3400930119778</t>
@@ -11705,7 +12865,11 @@
       <c r="P295" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr"/>
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>3001806</t>
+        </is>
+      </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
           <t>3400930018064</t>
@@ -11743,7 +12907,11 @@
       <c r="P296" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr"/>
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>4232919</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr"/>
       <c r="C297" s="2" t="inlineStr">
         <is>
@@ -11781,7 +12949,11 @@
       <c r="P297" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr"/>
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>3352113</t>
+        </is>
+      </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
           <t>3400933521134</t>
@@ -11819,7 +12991,11 @@
       <c r="P298" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr"/>
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>3593101</t>
+        </is>
+      </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
           <t>3400935931016</t>
@@ -11857,7 +13033,11 @@
       <c r="P299" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr"/>
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>3493670</t>
+        </is>
+      </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
           <t>3400934936708</t>
@@ -11895,7 +13075,11 @@
       <c r="P300" t="inlineStr"/>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr"/>
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>3369651</t>
+        </is>
+      </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
           <t>3400933696511</t>
@@ -11933,7 +13117,11 @@
       <c r="P301" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr"/>
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>3009071</t>
+        </is>
+      </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
           <t>3400930090718</t>
@@ -11971,7 +13159,11 @@
       <c r="P302" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr"/>
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>3174723</t>
+        </is>
+      </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
           <t>3400931747239</t>
@@ -12009,7 +13201,11 @@
       <c r="P303" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" t="inlineStr"/>
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>3245400</t>
+        </is>
+      </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
           <t>3400932454006</t>
@@ -12047,7 +13243,11 @@
       <c r="P304" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr"/>
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>3367037</t>
+        </is>
+      </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
           <t>3400933670375</t>
@@ -12085,7 +13285,11 @@
       <c r="P305" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr"/>
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>4948351</t>
+        </is>
+      </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
           <t>3400949483518</t>
@@ -12123,7 +13327,11 @@
       <c r="P306" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr"/>
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>3001398</t>
+        </is>
+      </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
           <t>3400930013984</t>
@@ -12161,7 +13369,11 @@
       <c r="P307" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr"/>
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>2678350</t>
+        </is>
+      </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
           <t>3400926783501</t>
@@ -12177,7 +13389,7 @@
         <v>302.95</v>
       </c>
       <c r="F308" s="3" t="n">
-        <v>291.17</v>
+        <v>291.2</v>
       </c>
       <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr"/>
@@ -12199,7 +13411,11 @@
       <c r="P308" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr"/>
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>3565062</t>
+        </is>
+      </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
           <t>3400935650627</t>
@@ -12237,7 +13453,11 @@
       <c r="P309" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" t="inlineStr"/>
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>3122689</t>
+        </is>
+      </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
           <t>3400931226895</t>
@@ -12275,7 +13495,11 @@
       <c r="P310" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr"/>
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>3770129</t>
+        </is>
+      </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
           <t>3400937701297</t>
@@ -12313,7 +13537,11 @@
       <c r="P311" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr"/>
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>3242028</t>
+        </is>
+      </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
           <t>3400932420285</t>
@@ -12351,7 +13579,11 @@
       <c r="P312" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr"/>
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>3172380</t>
+        </is>
+      </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
           <t>3400931723806</t>
@@ -12389,7 +13621,11 @@
       <c r="P313" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" t="inlineStr"/>
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>4066993</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr"/>
       <c r="C314" s="2" t="inlineStr">
         <is>
@@ -12427,7 +13663,11 @@
       <c r="P314" t="inlineStr"/>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr"/>
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>9972489</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr"/>
       <c r="C315" s="2" t="inlineStr">
         <is>
@@ -12440,10 +13680,10 @@
         </is>
       </c>
       <c r="E315" s="3" t="n">
-        <v>29.25</v>
+        <v>28.84</v>
       </c>
       <c r="F315" s="3" t="n">
-        <v>29.25</v>
+        <v>28.84</v>
       </c>
       <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr"/>
@@ -12465,7 +13705,11 @@
       <c r="P315" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr"/>
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>3405329</t>
+        </is>
+      </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
           <t>3400934053290</t>
@@ -12503,7 +13747,11 @@
       <c r="P316" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" t="inlineStr"/>
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>3267092</t>
+        </is>
+      </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
           <t>3400932670925</t>
@@ -12541,7 +13789,11 @@
       <c r="P317" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr"/>
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>3429229</t>
+        </is>
+      </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
           <t>3400934292293</t>
@@ -12579,7 +13831,11 @@
       <c r="P318" t="inlineStr"/>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr"/>
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>3012146</t>
+        </is>
+      </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
           <t>3400930121467</t>
@@ -12595,7 +13851,7 @@
         <v>7.06</v>
       </c>
       <c r="F319" s="3" t="n">
-        <v>6.79</v>
+        <v>6.78</v>
       </c>
       <c r="G319" t="inlineStr"/>
       <c r="H319" t="inlineStr"/>
@@ -12617,7 +13873,11 @@
       <c r="P319" t="inlineStr"/>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr"/>
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>3011976</t>
+        </is>
+      </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
           <t>3400930119761</t>
@@ -12655,7 +13915,11 @@
       <c r="P320" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" t="inlineStr"/>
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>9798867</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr"/>
       <c r="C321" s="2" t="inlineStr">
         <is>
@@ -12693,7 +13957,11 @@
       <c r="P321" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr"/>
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>3257001</t>
+        </is>
+      </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
           <t>3400932570010</t>
@@ -12731,7 +13999,11 @@
       <c r="P322" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr"/>
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>9985782</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr"/>
       <c r="C323" s="2" t="inlineStr">
         <is>
@@ -12769,7 +14041,11 @@
       <c r="P323" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr"/>
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>6237857</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr"/>
       <c r="C324" s="2" t="inlineStr">
         <is>
@@ -12782,10 +14058,10 @@
         </is>
       </c>
       <c r="E324" s="3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="F324" s="3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr"/>
@@ -12807,7 +14083,11 @@
       <c r="P324" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr"/>
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>3321733</t>
+        </is>
+      </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
           <t>3400933217334</t>
@@ -12845,7 +14125,11 @@
       <c r="P325" t="inlineStr"/>
     </row>
     <row r="326">
-      <c r="A326" t="inlineStr"/>
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>3291328</t>
+        </is>
+      </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
           <t>3400932913282</t>
@@ -12883,7 +14167,11 @@
       <c r="P326" t="inlineStr"/>
     </row>
     <row r="327">
-      <c r="A327" t="inlineStr"/>
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>3529178</t>
+        </is>
+      </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
           <t>3400935291783</t>
@@ -12921,7 +14209,11 @@
       <c r="P327" t="inlineStr"/>
     </row>
     <row r="328">
-      <c r="A328" t="inlineStr"/>
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>3081996</t>
+        </is>
+      </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
           <t>3400930819968</t>
@@ -12959,7 +14251,11 @@
       <c r="P328" t="inlineStr"/>
     </row>
     <row r="329">
-      <c r="A329" t="inlineStr"/>
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>3364062</t>
+        </is>
+      </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
           <t>3400933640620</t>
@@ -12997,7 +14293,11 @@
       <c r="P329" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr"/>
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>3021860</t>
+        </is>
+      </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
           <t>3400930218600</t>
@@ -13035,7 +14335,11 @@
       <c r="P330" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" t="inlineStr"/>
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>3021407</t>
+        </is>
+      </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
           <t>3400930214077</t>
@@ -13073,7 +14377,11 @@
       <c r="P331" t="inlineStr"/>
     </row>
     <row r="332">
-      <c r="A332" t="inlineStr"/>
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>3015816</t>
+        </is>
+      </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
           <t>3400930158166</t>
@@ -13111,7 +14419,11 @@
       <c r="P332" t="inlineStr"/>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr"/>
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>3176277</t>
+        </is>
+      </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
           <t>3400931762775</t>
@@ -13149,7 +14461,11 @@
       <c r="P333" t="inlineStr"/>
     </row>
     <row r="334">
-      <c r="A334" t="inlineStr"/>
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>3867308</t>
+        </is>
+      </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
           <t>3400938673081</t>
@@ -13187,7 +14503,11 @@
       <c r="P334" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" t="inlineStr"/>
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>3499916</t>
+        </is>
+      </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
           <t>3400934999161</t>
@@ -13225,7 +14545,11 @@
       <c r="P335" t="inlineStr"/>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr"/>
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>3016228</t>
+        </is>
+      </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
           <t>3400930162286</t>
@@ -13263,7 +14587,11 @@
       <c r="P336" t="inlineStr"/>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr"/>
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>3318665</t>
+        </is>
+      </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
           <t>3400933186654</t>
@@ -13301,7 +14629,11 @@
       <c r="P337" t="inlineStr"/>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr"/>
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>3024421</t>
+        </is>
+      </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
           <t>3400930244210</t>
@@ -13317,7 +14649,7 @@
         <v>36.18</v>
       </c>
       <c r="F338" s="3" t="n">
-        <v>34.77</v>
+        <v>34.8</v>
       </c>
       <c r="G338" t="inlineStr"/>
       <c r="H338" t="inlineStr"/>
@@ -13339,7 +14671,11 @@
       <c r="P338" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" t="inlineStr"/>
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>3027902</t>
+        </is>
+      </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
           <t>3400930279021</t>
@@ -13377,7 +14713,11 @@
       <c r="P339" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr"/>
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>3026414</t>
+        </is>
+      </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
           <t>3400930264140</t>
@@ -13415,7 +14755,11 @@
       <c r="P340" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr"/>
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>3030593</t>
+        </is>
+      </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
           <t>3400930305935</t>
@@ -13453,7 +14797,11 @@
       <c r="P341" t="inlineStr"/>
     </row>
     <row r="342">
-      <c r="A342" t="inlineStr"/>
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>3397883</t>
+        </is>
+      </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
           <t>3400933978839</t>
@@ -13491,7 +14839,11 @@
       <c r="P342" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr"/>
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>3752249</t>
+        </is>
+      </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
           <t>3400937522496</t>
@@ -13529,7 +14881,11 @@
       <c r="P343" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr"/>
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>3311143</t>
+        </is>
+      </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
           <t>3400933111434</t>
@@ -13567,7 +14923,11 @@
       <c r="P344" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr"/>
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>2756239</t>
+        </is>
+      </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
           <t>3400927562396</t>
@@ -13605,7 +14965,11 @@
       <c r="P345" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr"/>
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>3001851</t>
+        </is>
+      </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
           <t>3400930018514</t>
@@ -13621,7 +14985,7 @@
         <v>141.25</v>
       </c>
       <c r="F346" s="3" t="n">
-        <v>135.76</v>
+        <v>135.78</v>
       </c>
       <c r="G346" t="inlineStr"/>
       <c r="H346" t="inlineStr"/>
@@ -13643,7 +15007,11 @@
       <c r="P346" t="inlineStr"/>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr"/>
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>3569309</t>
+        </is>
+      </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
           <t>3400935693099</t>
@@ -13659,7 +15027,7 @@
         <v>4.42</v>
       </c>
       <c r="F347" s="3" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="G347" t="inlineStr"/>
       <c r="H347" t="inlineStr"/>
@@ -13681,7 +15049,11 @@
       <c r="P347" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr"/>
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>3382924</t>
+        </is>
+      </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
           <t>3400933829247</t>
@@ -13697,7 +15069,7 @@
         <v>4.47</v>
       </c>
       <c r="F348" s="3" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="G348" t="inlineStr"/>
       <c r="H348" t="inlineStr"/>
@@ -13719,7 +15091,11 @@
       <c r="P348" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr"/>
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>3005987</t>
+        </is>
+      </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
           <t>3400930059876</t>
@@ -13757,7 +15133,11 @@
       <c r="P349" t="inlineStr"/>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr"/>
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>3031781</t>
+        </is>
+      </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
           <t>3400930317815</t>
@@ -13773,7 +15153,7 @@
         <v>136.5</v>
       </c>
       <c r="F350" s="3" t="n">
-        <v>131.19</v>
+        <v>131.21</v>
       </c>
       <c r="G350" t="inlineStr"/>
       <c r="H350" t="inlineStr"/>
@@ -13795,7 +15175,11 @@
       <c r="P350" t="inlineStr"/>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr"/>
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>2664997</t>
+        </is>
+      </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
           <t>3400926649975</t>
@@ -13833,7 +15217,11 @@
       <c r="P351" t="inlineStr"/>
     </row>
     <row r="352">
-      <c r="A352" t="inlineStr"/>
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>2756162</t>
+        </is>
+      </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
           <t>3400927561627</t>
@@ -13871,7 +15259,11 @@
       <c r="P352" t="inlineStr"/>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr"/>
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>3950110</t>
+        </is>
+      </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
           <t>3400939501109</t>
@@ -13909,7 +15301,11 @@
       <c r="P353" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" t="inlineStr"/>
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>3308106</t>
+        </is>
+      </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
           <t>3400933081065</t>
@@ -13947,7 +15343,11 @@
       <c r="P354" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" t="inlineStr"/>
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>3873071</t>
+        </is>
+      </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
           <t>3400938730715</t>
@@ -13985,7 +15385,11 @@
       <c r="P355" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr"/>
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>3008874</t>
+        </is>
+      </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
           <t>3400930088746</t>
@@ -14023,7 +15427,11 @@
       <c r="P356" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr"/>
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>3217214</t>
+        </is>
+      </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
           <t>3400932172146</t>
@@ -14061,7 +15469,11 @@
       <c r="P357" t="inlineStr"/>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr"/>
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>3115376</t>
+        </is>
+      </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
           <t>3400931153764</t>
@@ -14099,7 +15511,11 @@
       <c r="P358" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr"/>
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>3615883</t>
+        </is>
+      </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
           <t>3400936158832</t>
@@ -14137,7 +15553,11 @@
       <c r="P359" t="inlineStr"/>
     </row>
     <row r="360">
-      <c r="A360" t="inlineStr"/>
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>3553343</t>
+        </is>
+      </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
           <t>3400935533432</t>
@@ -14175,7 +15595,11 @@
       <c r="P360" t="inlineStr"/>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr"/>
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>3380888</t>
+        </is>
+      </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
           <t>3400933808884</t>
@@ -14213,7 +15637,11 @@
       <c r="P361" t="inlineStr"/>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr"/>
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>3001807</t>
+        </is>
+      </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
           <t>3400930018071</t>
@@ -14251,7 +15679,11 @@
       <c r="P362" t="inlineStr"/>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr"/>
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>3406033</t>
+        </is>
+      </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
           <t>3400934060335</t>
@@ -14289,7 +15721,11 @@
       <c r="P363" t="inlineStr"/>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr"/>
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>3870687</t>
+        </is>
+      </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
           <t>3400938706871</t>
@@ -14327,7 +15763,11 @@
       <c r="P364" t="inlineStr"/>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr"/>
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>3029295</t>
+        </is>
+      </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
           <t>3400930292952</t>
@@ -14343,7 +15783,7 @@
         <v>404.83</v>
       </c>
       <c r="F365" s="3" t="n">
-        <v>389.08</v>
+        <v>389.11</v>
       </c>
       <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr"/>
@@ -14365,7 +15805,11 @@
       <c r="P365" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" t="inlineStr"/>
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>3322916</t>
+        </is>
+      </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
           <t>3400933229160</t>
@@ -14403,7 +15847,11 @@
       <c r="P366" t="inlineStr"/>
     </row>
     <row r="367">
-      <c r="A367" t="inlineStr"/>
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>7395817</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr"/>
       <c r="C367" s="2" t="inlineStr">
         <is>
@@ -14441,7 +15889,11 @@
       <c r="P367" t="inlineStr"/>
     </row>
     <row r="368">
-      <c r="A368" t="inlineStr"/>
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>3379744</t>
+        </is>
+      </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
           <t>3400933797447</t>
@@ -14479,7 +15931,11 @@
       <c r="P368" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" t="inlineStr"/>
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>3280543</t>
+        </is>
+      </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
           <t>3400932805433</t>
@@ -14517,7 +15973,11 @@
       <c r="P369" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr"/>
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>3267904</t>
+        </is>
+      </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
           <t>3400932679041</t>
@@ -14555,7 +16015,11 @@
       <c r="P370" t="inlineStr"/>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr"/>
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>3049478</t>
+        </is>
+      </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
           <t>3400930494783</t>
@@ -14593,7 +16057,11 @@
       <c r="P371" t="inlineStr"/>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr"/>
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>3553395</t>
+        </is>
+      </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
           <t>3400935533951</t>
@@ -14631,7 +16099,11 @@
       <c r="P372" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr"/>
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>3565151</t>
+        </is>
+      </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
           <t>3400935651518</t>
@@ -14669,7 +16141,11 @@
       <c r="P373" t="inlineStr"/>
     </row>
     <row r="374">
-      <c r="A374" t="inlineStr"/>
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>3442804</t>
+        </is>
+      </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
           <t>3400934428043</t>
@@ -14707,7 +16183,11 @@
       <c r="P374" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" t="inlineStr"/>
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>3019936</t>
+        </is>
+      </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
           <t>3400930199367</t>
@@ -14723,7 +16203,7 @@
         <v>292.11</v>
       </c>
       <c r="F375" s="3" t="n">
-        <v>280.75</v>
+        <v>280.78</v>
       </c>
       <c r="G375" t="inlineStr"/>
       <c r="H375" t="inlineStr"/>
@@ -14745,7 +16225,11 @@
       <c r="P375" t="inlineStr"/>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr"/>
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>2799970</t>
+        </is>
+      </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
           <t>3400927999703</t>
@@ -14783,7 +16267,11 @@
       <c r="P376" t="inlineStr"/>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr"/>
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>3359598</t>
+        </is>
+      </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
           <t>3400933595982</t>
@@ -14821,7 +16309,11 @@
       <c r="P377" t="inlineStr"/>
     </row>
     <row r="378">
-      <c r="A378" t="inlineStr"/>
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>3011930</t>
+        </is>
+      </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
           <t>3400930119303</t>
@@ -14859,7 +16351,11 @@
       <c r="P378" t="inlineStr"/>
     </row>
     <row r="379">
-      <c r="A379" t="inlineStr"/>
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>3387873</t>
+        </is>
+      </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
           <t>3400933878733</t>
@@ -14897,7 +16393,11 @@
       <c r="P379" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" t="inlineStr"/>
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>3306998</t>
+        </is>
+      </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
           <t>3400933069988</t>
@@ -14935,7 +16435,11 @@
       <c r="P380" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" t="inlineStr"/>
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>3181373</t>
+        </is>
+      </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
           <t>3400931813736</t>
@@ -14973,7 +16477,11 @@
       <c r="P381" t="inlineStr"/>
     </row>
     <row r="382">
-      <c r="A382" t="inlineStr"/>
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>3018694</t>
+        </is>
+      </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
           <t>3400930186947</t>
@@ -15011,7 +16519,11 @@
       <c r="P382" t="inlineStr"/>
     </row>
     <row r="383">
-      <c r="A383" t="inlineStr"/>
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>2800012</t>
+        </is>
+      </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
           <t>3400928000125</t>
@@ -15049,7 +16561,11 @@
       <c r="P383" t="inlineStr"/>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr"/>
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>4788864</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr"/>
       <c r="C384" s="2" t="inlineStr">
         <is>
@@ -15062,10 +16578,10 @@
         </is>
       </c>
       <c r="E384" s="3" t="n">
-        <v>7.72</v>
+        <v>7.73</v>
       </c>
       <c r="F384" s="3" t="n">
-        <v>7.72</v>
+        <v>7.73</v>
       </c>
       <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr"/>
@@ -15087,7 +16603,11 @@
       <c r="P384" t="inlineStr"/>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr"/>
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>7493603</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr"/>
       <c r="C385" s="2" t="inlineStr">
         <is>
@@ -15125,7 +16645,11 @@
       <c r="P385" t="inlineStr"/>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr"/>
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>3031325</t>
+        </is>
+      </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
           <t>3400930313251</t>
@@ -15163,7 +16687,11 @@
       <c r="P386" t="inlineStr"/>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr"/>
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>3584585</t>
+        </is>
+      </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
           <t>3400935845856</t>
@@ -15201,7 +16729,11 @@
       <c r="P387" t="inlineStr"/>
     </row>
     <row r="388">
-      <c r="A388" t="inlineStr"/>
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>3327581</t>
+        </is>
+      </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
           <t>3400933275815</t>
@@ -15239,7 +16771,11 @@
       <c r="P388" t="inlineStr"/>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr"/>
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>3246049</t>
+        </is>
+      </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
           <t>3400932460496</t>
@@ -15277,7 +16813,11 @@
       <c r="P389" t="inlineStr"/>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr"/>
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>3148996</t>
+        </is>
+      </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
           <t>3400931489962</t>
@@ -15315,7 +16855,11 @@
       <c r="P390" t="inlineStr"/>
     </row>
     <row r="391">
-      <c r="A391" t="inlineStr"/>
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>3553952</t>
+        </is>
+      </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
           <t>3400935539526</t>
@@ -15353,7 +16897,11 @@
       <c r="P391" t="inlineStr"/>
     </row>
     <row r="392">
-      <c r="A392" t="inlineStr"/>
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>3006654</t>
+        </is>
+      </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
           <t>3400930066546</t>
@@ -15391,7 +16939,11 @@
       <c r="P392" t="inlineStr"/>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr"/>
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>3025040</t>
+        </is>
+      </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
           <t>3400930250402</t>
@@ -15429,7 +16981,11 @@
       <c r="P393" t="inlineStr"/>
     </row>
     <row r="394">
-      <c r="A394" t="inlineStr"/>
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>3016226</t>
+        </is>
+      </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
           <t>3400930162262</t>
@@ -15467,7 +17023,11 @@
       <c r="P394" t="inlineStr"/>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr"/>
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>3273112</t>
+        </is>
+      </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
           <t>3400932731121</t>
@@ -15505,7 +17065,11 @@
       <c r="P395" t="inlineStr"/>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr"/>
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>3003834</t>
+        </is>
+      </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
           <t>3400930038345</t>
@@ -15543,7 +17107,11 @@
       <c r="P396" t="inlineStr"/>
     </row>
     <row r="397">
-      <c r="A397" t="inlineStr"/>
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>3322075</t>
+        </is>
+      </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
           <t>3400933220754</t>
@@ -15581,7 +17149,11 @@
       <c r="P397" t="inlineStr"/>
     </row>
     <row r="398">
-      <c r="A398" t="inlineStr"/>
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>3260664</t>
+        </is>
+      </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
           <t>3400932606641</t>
@@ -15619,7 +17191,11 @@
       <c r="P398" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr"/>
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>2800087</t>
+        </is>
+      </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
           <t>3400928000873</t>
@@ -15657,7 +17233,11 @@
       <c r="P399" t="inlineStr"/>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr"/>
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>3344349</t>
+        </is>
+      </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
           <t>3400933443498</t>
@@ -15695,7 +17275,11 @@
       <c r="P400" t="inlineStr"/>
     </row>
     <row r="401">
-      <c r="A401" t="inlineStr"/>
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>3304746</t>
+        </is>
+      </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
           <t>3400933047467</t>
@@ -15733,7 +17317,11 @@
       <c r="P401" t="inlineStr"/>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr"/>
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>3595270</t>
+        </is>
+      </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
           <t>3400935952707</t>
@@ -15749,7 +17337,7 @@
         <v>46.66</v>
       </c>
       <c r="F402" s="3" t="n">
-        <v>44.84</v>
+        <v>44.85</v>
       </c>
       <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr"/>
@@ -15771,7 +17359,11 @@
       <c r="P402" t="inlineStr"/>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr"/>
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>3431321</t>
+        </is>
+      </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
           <t>3400934313219</t>
@@ -15809,7 +17401,11 @@
       <c r="P403" t="inlineStr"/>
     </row>
     <row r="404">
-      <c r="A404" t="inlineStr"/>
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>3008113</t>
+        </is>
+      </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
           <t>3400930081136</t>
@@ -15847,7 +17443,11 @@
       <c r="P404" t="inlineStr"/>
     </row>
     <row r="405">
-      <c r="A405" t="inlineStr"/>
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>3222770</t>
+        </is>
+      </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
           <t>3400932227709</t>
@@ -15885,7 +17485,11 @@
       <c r="P405" t="inlineStr"/>
     </row>
     <row r="406">
-      <c r="A406" t="inlineStr"/>
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>3611106</t>
+        </is>
+      </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
           <t>3400936111066</t>
@@ -15923,7 +17527,11 @@
       <c r="P406" t="inlineStr"/>
     </row>
     <row r="407">
-      <c r="A407" t="inlineStr"/>
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>3115755</t>
+        </is>
+      </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
           <t>3400931157557</t>
@@ -15999,7 +17607,11 @@
       <c r="P408" t="inlineStr"/>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr"/>
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>3719648</t>
+        </is>
+      </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
           <t>3400937196482</t>
@@ -16037,7 +17649,11 @@
       <c r="P409" t="inlineStr"/>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr"/>
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>2756647</t>
+        </is>
+      </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
           <t>3400927566479</t>
@@ -16075,7 +17691,11 @@
       <c r="P410" t="inlineStr"/>
     </row>
     <row r="411">
-      <c r="A411" t="inlineStr"/>
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>3295533</t>
+        </is>
+      </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
           <t>3400932955336</t>
@@ -16113,7 +17733,11 @@
       <c r="P411" t="inlineStr"/>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr"/>
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>3385124</t>
+        </is>
+      </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
           <t>3400933851248</t>
@@ -16151,7 +17775,11 @@
       <c r="P412" t="inlineStr"/>
     </row>
     <row r="413">
-      <c r="A413" t="inlineStr"/>
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>2800041</t>
+        </is>
+      </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
           <t>3400928000415</t>
@@ -16189,7 +17817,11 @@
       <c r="P413" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr"/>
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>3010493</t>
+        </is>
+      </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
           <t>3400930104934</t>
@@ -16227,7 +17859,11 @@
       <c r="P414" t="inlineStr"/>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr"/>
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>3396955</t>
+        </is>
+      </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
           <t>3400933969554</t>
@@ -16265,7 +17901,11 @@
       <c r="P415" t="inlineStr"/>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr"/>
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>2794642</t>
+        </is>
+      </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
           <t>3400927946424</t>
@@ -16303,7 +17943,11 @@
       <c r="P416" t="inlineStr"/>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr"/>
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>9641315</t>
+        </is>
+      </c>
       <c r="B417" t="inlineStr"/>
       <c r="C417" s="2" t="inlineStr">
         <is>
@@ -16341,7 +17985,11 @@
       <c r="P417" t="inlineStr"/>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr"/>
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>2192305</t>
+        </is>
+      </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
           <t>3400921923056</t>
@@ -16379,7 +18027,11 @@
       <c r="P418" t="inlineStr"/>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr"/>
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>3589967</t>
+        </is>
+      </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
           <t>3400935899675</t>
@@ -16417,7 +18069,11 @@
       <c r="P419" t="inlineStr"/>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr"/>
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>3014606</t>
+        </is>
+      </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
           <t>3400930146064</t>
@@ -16455,7 +18111,11 @@
       <c r="P420" t="inlineStr"/>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr"/>
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>3011764</t>
+        </is>
+      </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
           <t>3400930117644</t>
@@ -16493,7 +18153,11 @@
       <c r="P421" t="inlineStr"/>
     </row>
     <row r="422">
-      <c r="A422" t="inlineStr"/>
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>3014999</t>
+        </is>
+      </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
           <t>3400930149997</t>
@@ -16506,10 +18170,10 @@
         </is>
       </c>
       <c r="E422" s="3" t="n">
-        <v>23.96</v>
+        <v>23.5</v>
       </c>
       <c r="F422" s="3" t="n">
-        <v>23.96</v>
+        <v>23.5</v>
       </c>
       <c r="G422" t="inlineStr"/>
       <c r="H422" t="inlineStr"/>
@@ -16531,7 +18195,11 @@
       <c r="P422" t="inlineStr"/>
     </row>
     <row r="423">
-      <c r="A423" t="inlineStr"/>
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>3312734</t>
+        </is>
+      </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
           <t>3400933127343</t>
@@ -16569,7 +18237,11 @@
       <c r="P423" t="inlineStr"/>
     </row>
     <row r="424">
-      <c r="A424" t="inlineStr"/>
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>3031146</t>
+        </is>
+      </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
           <t>3400930311462</t>
@@ -16585,7 +18257,7 @@
         <v>52.31</v>
       </c>
       <c r="F424" s="3" t="n">
-        <v>50.28</v>
+        <v>50.3</v>
       </c>
       <c r="G424" t="inlineStr"/>
       <c r="H424" t="inlineStr"/>
@@ -16607,7 +18279,11 @@
       <c r="P424" t="inlineStr"/>
     </row>
     <row r="425">
-      <c r="A425" t="inlineStr"/>
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>3022503</t>
+        </is>
+      </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
           <t>3400930225035</t>
@@ -16645,7 +18321,11 @@
       <c r="P425" t="inlineStr"/>
     </row>
     <row r="426">
-      <c r="A426" t="inlineStr"/>
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>3015286</t>
+        </is>
+      </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
           <t>3400930152867</t>
@@ -16683,7 +18363,11 @@
       <c r="P426" t="inlineStr"/>
     </row>
     <row r="427">
-      <c r="A427" t="inlineStr"/>
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>3392236</t>
+        </is>
+      </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
           <t>3400933922368</t>
@@ -16721,7 +18405,11 @@
       <c r="P427" t="inlineStr"/>
     </row>
     <row r="428">
-      <c r="A428" t="inlineStr"/>
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>3338685</t>
+        </is>
+      </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
           <t>3400933386856</t>
@@ -16759,7 +18447,11 @@
       <c r="P428" t="inlineStr"/>
     </row>
     <row r="429">
-      <c r="A429" t="inlineStr"/>
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>3230924</t>
+        </is>
+      </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
           <t>3400932309245</t>
@@ -16797,7 +18489,11 @@
       <c r="P429" t="inlineStr"/>
     </row>
     <row r="430">
-      <c r="A430" t="inlineStr"/>
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>3517904</t>
+        </is>
+      </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
           <t>3400935179043</t>
@@ -16835,7 +18531,11 @@
       <c r="P430" t="inlineStr"/>
     </row>
     <row r="431">
-      <c r="A431" t="inlineStr"/>
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>3170524</t>
+        </is>
+      </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
           <t>3400931705246</t>
@@ -16873,7 +18573,11 @@
       <c r="P431" t="inlineStr"/>
     </row>
     <row r="432">
-      <c r="A432" t="inlineStr"/>
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>3379750</t>
+        </is>
+      </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
           <t>3400933797508</t>
@@ -16911,7 +18615,11 @@
       <c r="P432" t="inlineStr"/>
     </row>
     <row r="433">
-      <c r="A433" t="inlineStr"/>
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>3021939</t>
+        </is>
+      </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
           <t>3400930219393</t>
@@ -16949,7 +18657,11 @@
       <c r="P433" t="inlineStr"/>
     </row>
     <row r="434">
-      <c r="A434" t="inlineStr"/>
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>3476720</t>
+        </is>
+      </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
           <t>3400934767203</t>
@@ -16965,7 +18677,7 @@
         <v>4.35</v>
       </c>
       <c r="F434" s="3" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr"/>
@@ -16987,7 +18699,11 @@
       <c r="P434" t="inlineStr"/>
     </row>
     <row r="435">
-      <c r="A435" t="inlineStr"/>
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>3208250</t>
+        </is>
+      </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
           <t>3400932082506</t>
@@ -17025,7 +18741,11 @@
       <c r="P435" t="inlineStr"/>
     </row>
     <row r="436">
-      <c r="A436" t="inlineStr"/>
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>3001069</t>
+        </is>
+      </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
           <t>3400930010693</t>
@@ -17063,7 +18783,11 @@
       <c r="P436" t="inlineStr"/>
     </row>
     <row r="437">
-      <c r="A437" t="inlineStr"/>
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>3024344</t>
+        </is>
+      </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
           <t>3400930243442</t>
@@ -17101,7 +18825,11 @@
       <c r="P437" t="inlineStr"/>
     </row>
     <row r="438">
-      <c r="A438" t="inlineStr"/>
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>3421713</t>
+        </is>
+      </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
           <t>3400934217135</t>
@@ -17139,7 +18867,11 @@
       <c r="P438" t="inlineStr"/>
     </row>
     <row r="439">
-      <c r="A439" t="inlineStr"/>
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>3006656</t>
+        </is>
+      </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
           <t>3400930066560</t>
@@ -17215,7 +18947,11 @@
       <c r="P440" t="inlineStr"/>
     </row>
     <row r="441">
-      <c r="A441" t="inlineStr"/>
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>3085244</t>
+        </is>
+      </c>
       <c r="B441" s="2" t="inlineStr">
         <is>
           <t>3400930852446</t>
@@ -17253,7 +18989,11 @@
       <c r="P441" t="inlineStr"/>
     </row>
     <row r="442">
-      <c r="A442" t="inlineStr"/>
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>3410543</t>
+        </is>
+      </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
           <t>3400934105432</t>
@@ -17291,7 +19031,11 @@
       <c r="P442" t="inlineStr"/>
     </row>
     <row r="443">
-      <c r="A443" t="inlineStr"/>
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>5204026</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr"/>
       <c r="C443" s="2" t="inlineStr">
         <is>
@@ -17329,7 +19073,11 @@
       <c r="P443" t="inlineStr"/>
     </row>
     <row r="444">
-      <c r="A444" t="inlineStr"/>
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>3002334</t>
+        </is>
+      </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
           <t>3400930023341</t>
@@ -17367,7 +19115,11 @@
       <c r="P444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" t="inlineStr"/>
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>3547934</t>
+        </is>
+      </c>
       <c r="B445" s="2" t="inlineStr">
         <is>
           <t>3400935479341</t>
@@ -17405,7 +19157,11 @@
       <c r="P445" t="inlineStr"/>
     </row>
     <row r="446">
-      <c r="A446" t="inlineStr"/>
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>3042513</t>
+        </is>
+      </c>
       <c r="B446" s="2" t="inlineStr">
         <is>
           <t>3400930425138</t>
@@ -17443,7 +19199,11 @@
       <c r="P446" t="inlineStr"/>
     </row>
     <row r="447">
-      <c r="A447" t="inlineStr"/>
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>3699294</t>
+        </is>
+      </c>
       <c r="B447" s="2" t="inlineStr">
         <is>
           <t>3400936992948</t>
@@ -17481,7 +19241,11 @@
       <c r="P447" t="inlineStr"/>
     </row>
     <row r="448">
-      <c r="A448" t="inlineStr"/>
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>3474856</t>
+        </is>
+      </c>
       <c r="B448" s="2" t="inlineStr">
         <is>
           <t>3400934748561</t>
@@ -17519,7 +19283,11 @@
       <c r="P448" t="inlineStr"/>
     </row>
     <row r="449">
-      <c r="A449" t="inlineStr"/>
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>5202702</t>
+        </is>
+      </c>
       <c r="B449" t="inlineStr"/>
       <c r="C449" s="2" t="inlineStr">
         <is>
@@ -17557,7 +19325,11 @@
       <c r="P449" t="inlineStr"/>
     </row>
     <row r="450">
-      <c r="A450" t="inlineStr"/>
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>3705445</t>
+        </is>
+      </c>
       <c r="B450" s="2" t="inlineStr">
         <is>
           <t>3400937054454</t>
@@ -17595,7 +19367,11 @@
       <c r="P450" t="inlineStr"/>
     </row>
     <row r="451">
-      <c r="A451" t="inlineStr"/>
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>3811265</t>
+        </is>
+      </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
           <t>3400938112658</t>
@@ -17611,7 +19387,7 @@
         <v>4.35</v>
       </c>
       <c r="F451" s="3" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr"/>
@@ -17633,7 +19409,11 @@
       <c r="P451" t="inlineStr"/>
     </row>
     <row r="452">
-      <c r="A452" t="inlineStr"/>
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>3184087</t>
+        </is>
+      </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
           <t>3400931840879</t>
@@ -17671,7 +19451,11 @@
       <c r="P452" t="inlineStr"/>
     </row>
     <row r="453">
-      <c r="A453" t="inlineStr"/>
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>2238220</t>
+        </is>
+      </c>
       <c r="B453" s="2" t="inlineStr">
         <is>
           <t>3400922382203</t>
@@ -17709,7 +19493,11 @@
       <c r="P453" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" t="inlineStr"/>
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>3332352</t>
+        </is>
+      </c>
       <c r="B454" s="2" t="inlineStr">
         <is>
           <t>3400933323523</t>
@@ -17722,10 +19510,10 @@
         </is>
       </c>
       <c r="E454" s="3" t="n">
-        <v>3.22</v>
+        <v>2.84</v>
       </c>
       <c r="F454" s="3" t="n">
-        <v>3.04</v>
+        <v>2.66</v>
       </c>
       <c r="G454" t="inlineStr"/>
       <c r="H454" t="inlineStr"/>
@@ -17747,7 +19535,11 @@
       <c r="P454" t="inlineStr"/>
     </row>
     <row r="455">
-      <c r="A455" t="inlineStr"/>
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>3352538</t>
+        </is>
+      </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
           <t>3400933525385</t>
@@ -17785,7 +19577,11 @@
       <c r="P455" t="inlineStr"/>
     </row>
     <row r="456">
-      <c r="A456" t="inlineStr"/>
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>3022301</t>
+        </is>
+      </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
           <t>3400930223017</t>
@@ -17801,7 +19597,7 @@
         <v>47.86</v>
       </c>
       <c r="F456" s="3" t="n">
-        <v>46</v>
+        <v>46.02</v>
       </c>
       <c r="G456" t="inlineStr"/>
       <c r="H456" t="inlineStr"/>
@@ -17823,7 +19619,11 @@
       <c r="P456" t="inlineStr"/>
     </row>
     <row r="457">
-      <c r="A457" t="inlineStr"/>
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>3019564</t>
+        </is>
+      </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
           <t>3400930195642</t>
@@ -17861,7 +19661,11 @@
       <c r="P457" t="inlineStr"/>
     </row>
     <row r="458">
-      <c r="A458" t="inlineStr"/>
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>2110454</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr"/>
       <c r="C458" s="2" t="inlineStr">
         <is>
@@ -17899,7 +19703,11 @@
       <c r="P458" t="inlineStr"/>
     </row>
     <row r="459">
-      <c r="A459" t="inlineStr"/>
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>3990115</t>
+        </is>
+      </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
           <t>3400939901152</t>
@@ -17915,7 +19723,7 @@
         <v>45.12</v>
       </c>
       <c r="F459" s="3" t="n">
-        <v>43.36</v>
+        <v>43.39</v>
       </c>
       <c r="G459" t="inlineStr"/>
       <c r="H459" t="inlineStr"/>
@@ -17937,7 +19745,11 @@
       <c r="P459" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" t="inlineStr"/>
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>4200873</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr"/>
       <c r="C460" s="2" t="inlineStr">
         <is>
@@ -17975,7 +19787,11 @@
       <c r="P460" t="inlineStr"/>
     </row>
     <row r="461">
-      <c r="A461" t="inlineStr"/>
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>4453342</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr"/>
       <c r="C461" s="2" t="inlineStr">
         <is>
@@ -18013,7 +19829,11 @@
       <c r="P461" t="inlineStr"/>
     </row>
     <row r="462">
-      <c r="A462" t="inlineStr"/>
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>3495137</t>
+        </is>
+      </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
           <t>3400934951374</t>
@@ -18026,10 +19846,10 @@
         </is>
       </c>
       <c r="E462" s="3" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="F462" s="3" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="G462" t="inlineStr"/>
       <c r="H462" t="inlineStr"/>
@@ -18051,7 +19871,11 @@
       <c r="P462" t="inlineStr"/>
     </row>
     <row r="463">
-      <c r="A463" t="inlineStr"/>
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>3020207</t>
+        </is>
+      </c>
       <c r="B463" s="2" t="inlineStr">
         <is>
           <t>3400930202074</t>
@@ -18089,7 +19913,11 @@
       <c r="P463" t="inlineStr"/>
     </row>
     <row r="464">
-      <c r="A464" t="inlineStr"/>
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>3077144</t>
+        </is>
+      </c>
       <c r="B464" s="2" t="inlineStr">
         <is>
           <t>3400930771440</t>
@@ -18105,7 +19933,7 @@
         <v>9.9</v>
       </c>
       <c r="F464" s="3" t="n">
-        <v>9.51</v>
+        <v>9.52</v>
       </c>
       <c r="G464" t="inlineStr"/>
       <c r="H464" t="inlineStr"/>
@@ -18127,7 +19955,11 @@
       <c r="P464" t="inlineStr"/>
     </row>
     <row r="465">
-      <c r="A465" t="inlineStr"/>
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>3634461</t>
+        </is>
+      </c>
       <c r="B465" s="2" t="inlineStr">
         <is>
           <t>3400936344617</t>
@@ -18165,7 +19997,11 @@
       <c r="P465" t="inlineStr"/>
     </row>
     <row r="466">
-      <c r="A466" t="inlineStr"/>
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>3042536</t>
+        </is>
+      </c>
       <c r="B466" s="2" t="inlineStr">
         <is>
           <t>3400930425367</t>
@@ -18203,7 +20039,11 @@
       <c r="P466" t="inlineStr"/>
     </row>
     <row r="467">
-      <c r="A467" t="inlineStr"/>
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>3022518</t>
+        </is>
+      </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
           <t>3400930225189</t>
@@ -18241,7 +20081,11 @@
       <c r="P467" t="inlineStr"/>
     </row>
     <row r="468">
-      <c r="A468" t="inlineStr"/>
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>3013974</t>
+        </is>
+      </c>
       <c r="B468" s="2" t="inlineStr">
         <is>
           <t>3400930139745</t>
@@ -18279,7 +20123,11 @@
       <c r="P468" t="inlineStr"/>
     </row>
     <row r="469">
-      <c r="A469" t="inlineStr"/>
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>3639553</t>
+        </is>
+      </c>
       <c r="B469" s="2" t="inlineStr">
         <is>
           <t>3400936395534</t>
@@ -18295,7 +20143,7 @@
         <v>17.63</v>
       </c>
       <c r="F469" s="3" t="n">
-        <v>16.94</v>
+        <v>16.95</v>
       </c>
       <c r="G469" t="inlineStr"/>
       <c r="H469" t="inlineStr"/>
@@ -18317,7 +20165,11 @@
       <c r="P469" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" t="inlineStr"/>
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>3022190</t>
+        </is>
+      </c>
       <c r="B470" s="2" t="inlineStr">
         <is>
           <t>3400930221907</t>
@@ -18355,7 +20207,11 @@
       <c r="P470" t="inlineStr"/>
     </row>
     <row r="471">
-      <c r="A471" t="inlineStr"/>
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>3690904</t>
+        </is>
+      </c>
       <c r="B471" s="2" t="inlineStr">
         <is>
           <t>3400936909045</t>
@@ -18393,7 +20249,11 @@
       <c r="P471" t="inlineStr"/>
     </row>
     <row r="472">
-      <c r="A472" t="inlineStr"/>
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>3022512</t>
+        </is>
+      </c>
       <c r="B472" s="2" t="inlineStr">
         <is>
           <t>3400930225127</t>
@@ -18431,7 +20291,11 @@
       <c r="P472" t="inlineStr"/>
     </row>
     <row r="473">
-      <c r="A473" t="inlineStr"/>
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>3291819</t>
+        </is>
+      </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
           <t>3400932918195</t>
@@ -18444,10 +20308,10 @@
         </is>
       </c>
       <c r="E473" s="3" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="F473" s="3" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G473" t="inlineStr"/>
       <c r="H473" t="inlineStr"/>
@@ -18469,7 +20333,11 @@
       <c r="P473" t="inlineStr"/>
     </row>
     <row r="474">
-      <c r="A474" t="inlineStr"/>
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>3431858</t>
+        </is>
+      </c>
       <c r="B474" s="2" t="inlineStr">
         <is>
           <t>3400934318580</t>
@@ -18507,7 +20375,11 @@
       <c r="P474" t="inlineStr"/>
     </row>
     <row r="475">
-      <c r="A475" t="inlineStr"/>
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>3010708</t>
+        </is>
+      </c>
       <c r="B475" s="2" t="inlineStr">
         <is>
           <t>3400930107089</t>
@@ -18545,7 +20417,11 @@
       <c r="P475" t="inlineStr"/>
     </row>
     <row r="476">
-      <c r="A476" t="inlineStr"/>
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>3008416</t>
+        </is>
+      </c>
       <c r="B476" s="2" t="inlineStr">
         <is>
           <t>3400930084168</t>
@@ -18561,7 +20437,7 @@
         <v>41.27</v>
       </c>
       <c r="F476" s="3" t="n">
-        <v>39.66</v>
+        <v>39.67</v>
       </c>
       <c r="G476" t="inlineStr"/>
       <c r="H476" t="inlineStr"/>
@@ -18583,7 +20459,11 @@
       <c r="P476" t="inlineStr"/>
     </row>
     <row r="477">
-      <c r="A477" t="inlineStr"/>
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>4190836</t>
+        </is>
+      </c>
       <c r="B477" s="2" t="inlineStr">
         <is>
           <t>3400941908361</t>
@@ -18621,7 +20501,11 @@
       <c r="P477" t="inlineStr"/>
     </row>
     <row r="478">
-      <c r="A478" t="inlineStr"/>
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>3418869</t>
+        </is>
+      </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
           <t>3400934188695</t>
@@ -18634,10 +20518,10 @@
         </is>
       </c>
       <c r="E478" s="3" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="F478" s="3" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="G478" t="inlineStr"/>
       <c r="H478" t="inlineStr"/>
@@ -18659,7 +20543,11 @@
       <c r="P478" t="inlineStr"/>
     </row>
     <row r="479">
-      <c r="A479" t="inlineStr"/>
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>2792962</t>
+        </is>
+      </c>
       <c r="B479" s="2" t="inlineStr">
         <is>
           <t>3400927929625</t>
@@ -18697,7 +20585,11 @@
       <c r="P479" t="inlineStr"/>
     </row>
     <row r="480">
-      <c r="A480" t="inlineStr"/>
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>3194915</t>
+        </is>
+      </c>
       <c r="B480" s="2" t="inlineStr">
         <is>
           <t>3400931949152</t>
@@ -18735,7 +20627,11 @@
       <c r="P480" t="inlineStr"/>
     </row>
     <row r="481">
-      <c r="A481" t="inlineStr"/>
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>3027603</t>
+        </is>
+      </c>
       <c r="B481" s="2" t="inlineStr">
         <is>
           <t>3400930276037</t>
@@ -18773,7 +20669,11 @@
       <c r="P481" t="inlineStr"/>
     </row>
     <row r="482">
-      <c r="A482" t="inlineStr"/>
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>3270361</t>
+        </is>
+      </c>
       <c r="B482" s="2" t="inlineStr">
         <is>
           <t>3400932703616</t>
@@ -18811,7 +20711,11 @@
       <c r="P482" t="inlineStr"/>
     </row>
     <row r="483">
-      <c r="A483" t="inlineStr"/>
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>7395823</t>
+        </is>
+      </c>
       <c r="B483" t="inlineStr"/>
       <c r="C483" s="2" t="inlineStr">
         <is>
@@ -18849,7 +20753,11 @@
       <c r="P483" t="inlineStr"/>
     </row>
     <row r="484">
-      <c r="A484" t="inlineStr"/>
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>3017385</t>
+        </is>
+      </c>
       <c r="B484" s="2" t="inlineStr">
         <is>
           <t>3400930173855</t>
@@ -18887,7 +20795,11 @@
       <c r="P484" t="inlineStr"/>
     </row>
     <row r="485">
-      <c r="A485" t="inlineStr"/>
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>3911156</t>
+        </is>
+      </c>
       <c r="B485" s="2" t="inlineStr">
         <is>
           <t>3400939111568</t>
@@ -18925,7 +20837,11 @@
       <c r="P485" t="inlineStr"/>
     </row>
     <row r="486">
-      <c r="A486" t="inlineStr"/>
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>3026259</t>
+        </is>
+      </c>
       <c r="B486" s="2" t="inlineStr">
         <is>
           <t>3400930262597</t>
@@ -18941,7 +20857,7 @@
         <v>349.93</v>
       </c>
       <c r="F486" s="3" t="n">
-        <v>336.32</v>
+        <v>336.35</v>
       </c>
       <c r="G486" t="inlineStr"/>
       <c r="H486" t="inlineStr"/>
@@ -18963,7 +20879,11 @@
       <c r="P486" t="inlineStr"/>
     </row>
     <row r="487">
-      <c r="A487" t="inlineStr"/>
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>3021967</t>
+        </is>
+      </c>
       <c r="B487" s="2" t="inlineStr">
         <is>
           <t>3400930219676</t>
@@ -18979,7 +20899,7 @@
         <v>7.05</v>
       </c>
       <c r="F487" s="3" t="n">
-        <v>6.78</v>
+        <v>6.77</v>
       </c>
       <c r="G487" t="inlineStr"/>
       <c r="H487" t="inlineStr"/>
@@ -19001,7 +20921,11 @@
       <c r="P487" t="inlineStr"/>
     </row>
     <row r="488">
-      <c r="A488" t="inlineStr"/>
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>3616279</t>
+        </is>
+      </c>
       <c r="B488" s="2" t="inlineStr">
         <is>
           <t>3400936162792</t>
@@ -19039,7 +20963,11 @@
       <c r="P488" t="inlineStr"/>
     </row>
     <row r="489">
-      <c r="A489" t="inlineStr"/>
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>3260670</t>
+        </is>
+      </c>
       <c r="B489" s="2" t="inlineStr">
         <is>
           <t>3400932606702</t>
@@ -19077,7 +21005,11 @@
       <c r="P489" t="inlineStr"/>
     </row>
     <row r="490">
-      <c r="A490" t="inlineStr"/>
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>3004003</t>
+        </is>
+      </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
           <t>3400930040034</t>
@@ -19093,7 +21025,7 @@
         <v>23.68</v>
       </c>
       <c r="F490" s="3" t="n">
-        <v>22.76</v>
+        <v>22.79</v>
       </c>
       <c r="G490" t="inlineStr"/>
       <c r="H490" t="inlineStr"/>
@@ -19115,7 +21047,11 @@
       <c r="P490" t="inlineStr"/>
     </row>
     <row r="491">
-      <c r="A491" t="inlineStr"/>
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>3091523</t>
+        </is>
+      </c>
       <c r="B491" s="2" t="inlineStr">
         <is>
           <t>3400930915233</t>
@@ -19153,7 +21089,11 @@
       <c r="P491" t="inlineStr"/>
     </row>
     <row r="492">
-      <c r="A492" t="inlineStr"/>
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>3275826</t>
+        </is>
+      </c>
       <c r="B492" s="2" t="inlineStr">
         <is>
           <t>3400932758265</t>
@@ -19204,10 +21144,10 @@
         </is>
       </c>
       <c r="E493" s="3" t="n">
-        <v>11.89</v>
+        <v>12.7</v>
       </c>
       <c r="F493" s="3" t="n">
-        <v>11.89</v>
+        <v>12.7</v>
       </c>
       <c r="G493" t="inlineStr"/>
       <c r="H493" t="inlineStr"/>
@@ -19229,7 +21169,11 @@
       <c r="P493" t="inlineStr"/>
     </row>
     <row r="494">
-      <c r="A494" t="inlineStr"/>
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>3350261</t>
+        </is>
+      </c>
       <c r="B494" s="2" t="inlineStr">
         <is>
           <t>3400933502614</t>
@@ -19267,7 +21211,11 @@
       <c r="P494" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" t="inlineStr"/>
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>3430706</t>
+        </is>
+      </c>
       <c r="B495" s="2" t="inlineStr">
         <is>
           <t>3400934307065</t>
@@ -19305,7 +21253,11 @@
       <c r="P495" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" t="inlineStr"/>
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>3748377</t>
+        </is>
+      </c>
       <c r="B496" s="2" t="inlineStr">
         <is>
           <t>3400937483773</t>
@@ -19343,7 +21295,11 @@
       <c r="P496" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" t="inlineStr"/>
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>3130329</t>
+        </is>
+      </c>
       <c r="B497" s="2" t="inlineStr">
         <is>
           <t>3400931303299</t>
@@ -19381,7 +21337,11 @@
       <c r="P497" t="inlineStr"/>
     </row>
     <row r="498">
-      <c r="A498" t="inlineStr"/>
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>2761111</t>
+        </is>
+      </c>
       <c r="B498" s="2" t="inlineStr">
         <is>
           <t>3400927611117</t>
@@ -19419,7 +21379,11 @@
       <c r="P498" t="inlineStr"/>
     </row>
     <row r="499">
-      <c r="A499" t="inlineStr"/>
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>3261304</t>
+        </is>
+      </c>
       <c r="B499" s="2" t="inlineStr">
         <is>
           <t>3400932613045</t>
@@ -19457,7 +21421,11 @@
       <c r="P499" t="inlineStr"/>
     </row>
     <row r="500">
-      <c r="A500" t="inlineStr"/>
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>3529103</t>
+        </is>
+      </c>
       <c r="B500" s="2" t="inlineStr">
         <is>
           <t>3400935291035</t>
@@ -19495,7 +21463,11 @@
       <c r="P500" t="inlineStr"/>
     </row>
     <row r="501">
-      <c r="A501" t="inlineStr"/>
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>3622452</t>
+        </is>
+      </c>
       <c r="B501" s="2" t="inlineStr">
         <is>
           <t>3400936224520</t>
@@ -19511,7 +21483,7 @@
         <v>22.71</v>
       </c>
       <c r="F501" s="3" t="n">
-        <v>21.83</v>
+        <v>21.85</v>
       </c>
       <c r="G501" t="inlineStr"/>
       <c r="H501" t="inlineStr"/>
